--- a/_doc/AppToolTip.xlsx
+++ b/_doc/AppToolTip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshi\FMKyuyo\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7E3F47-B643-4147-B4AE-66F962318BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7741E726-6CE7-428D-846D-F95010E82704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="2505" windowWidth="28800" windowHeight="15555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="28800" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>None</t>
   </si>
@@ -387,10 +387,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NotEnouthDigit</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>数値以外の文字が入力されています。</t>
     <rPh sb="0" eb="2">
       <t>スウチ</t>
@@ -408,121 +404,6 @@
   </si>
   <si>
     <t>OnlyNumber</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>個人番号は{0}桁で入力してください。</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ケタ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>桁数が不足しています。</t>
-    <rPh sb="0" eb="2">
-      <t>ケタスウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>フソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OutOfDateRange</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>月度内の日付を指定してください。</t>
-    <rPh sb="0" eb="2">
-      <t>ゲツド</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>範囲外の日付です。</t>
-    <rPh sb="0" eb="2">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ガイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒヅケ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CannotMonthCheckOff</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>月別手当として使用されているため、チェックをオフにする事はできません。</t>
-    <rPh sb="0" eb="2">
-      <t>ツキベツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>コト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>既に勤務データ入力で使用されています。</t>
-    <rPh sb="0" eb="1">
-      <t>スデ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キンム</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>IlligalMyNumber</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入力された個人番号は有効ではありません。</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ユウコウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -613,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -634,9 +515,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -942,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="26.25" style="1" bestFit="1" customWidth="1"/>
@@ -1144,10 +1022,10 @@
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>37</v>
@@ -1157,60 +1035,28 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A16" s="3"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
     </row>
     <row r="20" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3"/>
@@ -2525,30 +2371,6 @@
       <c r="B238" s="6"/>
       <c r="C238" s="6"/>
       <c r="D238" s="5"/>
-    </row>
-    <row r="239" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A239" s="3"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="6"/>
-      <c r="D239" s="5"/>
-    </row>
-    <row r="240" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A240" s="3"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="6"/>
-      <c r="D240" s="5"/>
-    </row>
-    <row r="241" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A241" s="3"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="6"/>
-      <c r="D241" s="5"/>
-    </row>
-    <row r="242" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A242" s="3"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="6"/>
-      <c r="D242" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
